--- a/Inquiries_12-10-2026.xlsx
+++ b/Inquiries_12-10-2026.xlsx
@@ -410,7 +410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69921875" defaultRowHeight="13.8"/>
   <cols>
     <col width="8.69921875" customWidth="1" style="2" min="1" max="3"/>
@@ -468,6 +468,34 @@
         <v>29.42068965517241</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>80.27482823235478</v>
+      </c>
+      <c r="D4" t="n">
+        <v>84.22570286388361</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>80.27482823235478</v>
+      </c>
+      <c r="D5" t="n">
+        <v>83.33549474776294</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
